--- a/Resources/excelTemplates/jobsTemplate.xlsx
+++ b/Resources/excelTemplates/jobsTemplate.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\GoldenAltos\Resources\excelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFFDD50-CDD2-4970-9D7A-8D0A57567387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30321FFC-9441-4AE9-ACA4-695CBE36F62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="All others" sheetId="1" r:id="rId1"/>
+    <sheet name="Jobs" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,28 +30,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -136,7 +114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -274,6 +252,134 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top style="medium">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -281,14 +387,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -296,20 +399,47 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -329,68 +459,59 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1114425</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1559510</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9E4456F-E84C-897C-ED4F-525CF42E3DB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1990725" y="0"/>
+          <a:ext cx="8248650" cy="1559510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -710,19 +831,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="8.5703125" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="12" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" customWidth="1"/>
     <col min="13" max="15" width="9.140625" customWidth="1"/>
     <col min="16" max="16" width="8.42578125" customWidth="1"/>
     <col min="17" max="19" width="9.140625" hidden="1" customWidth="1"/>
@@ -730,79 +853,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="127.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="7"/>
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:22" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="20"/>
+    </row>
+    <row r="3" spans="1:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="8"/>
-      <c r="U2" s="8"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="N11" s="5"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="N12" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.4" footer="0.4"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -811,5 +957,6 @@
     <oddFooter>Company Confidential.     Dated:8/4/2025 at 08:58:02    ANT
 Page: &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>